--- a/docs/downloads/11/tbl_cata_type_alaotra_analamiranga.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_analamiranga.xlsx
@@ -441,12 +441,6 @@
           <t>Rats</t>
         </is>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>8.699999999999999</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +453,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +465,6 @@
           <t>Maladie des cultures/élevage</t>
         </is>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -657,12 +639,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +651,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -692,12 +662,6 @@
         <is>
           <t>Criquets</t>
         </is>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
